--- a/实验一/实验一 alltest.s 内容分析.xlsx
+++ b/实验一/实验一 alltest.s 内容分析.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\计算机体系结构\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\计算机体系结构\实验一\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEA054DC-FE8D-4B78-93F9-84AF7E814B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92234BC8-0370-494F-8719-23AC6AA916DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3228" yWindow="3096" windowWidth="22764" windowHeight="12036" xr2:uid="{9DA4EB76-4933-42EB-BEC1-5E0EA9C8598E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9DA4EB76-4933-42EB-BEC1-5E0EA9C8598E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="108">
   <si>
     <t># load和store指令</t>
   </si>
@@ -202,13 +202,208 @@
   <si>
     <t>解释指令执行导致变化的原因</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000004</t>
+  </si>
+  <si>
+    <t>0x0000000000000000</t>
+  </si>
+  <si>
+    <t>0x000000000000007C</t>
+  </si>
+  <si>
+    <t>不变</t>
+  </si>
+  <si>
+    <t>不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0000000000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000008</t>
+  </si>
+  <si>
+    <t>0xFFFFFFFFFFFFFF80</t>
+  </si>
+  <si>
+    <t>0x0000000C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0000000000000080</t>
+  </si>
+  <si>
+    <t>0x000000000000007C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0000000000000080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000020</t>
+  </si>
+  <si>
+    <t>0x00000018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000024</t>
+  </si>
+  <si>
+    <t>0x00000028</t>
+  </si>
+  <si>
+    <t>0x00000030</t>
+  </si>
+  <si>
+    <t>0x00000034</t>
+  </si>
+  <si>
+    <t>0x00000038</t>
+  </si>
+  <si>
+    <t>0x00000040</t>
+  </si>
+  <si>
+    <t>0x00000044</t>
+  </si>
+  <si>
+    <t>0x00000048</t>
+  </si>
+  <si>
+    <t>0x0000004C</t>
+  </si>
+  <si>
+    <t>0x00000058</t>
+  </si>
+  <si>
+    <t>0x00000064</t>
+  </si>
+  <si>
+    <t>0x000000000000005C</t>
+  </si>
+  <si>
+    <t>0x00000068</t>
+  </si>
+  <si>
+    <t>0x0000000000000074</t>
+  </si>
+  <si>
+    <t>0x00000074</t>
+  </si>
+  <si>
+    <t>0x000000000000006C</t>
+  </si>
+  <si>
+    <t>读取DATA，不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFFER处值300变为128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00000078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 DATA 的地址 0x7C 加到 r0 后写入 r8，使 r8 指向 DATA</t>
+  </si>
+  <si>
+    <t>从 r8 指向的内存读取 1 字节 0x80。LB 按有符号数进行符号扩展，得到 0xFFFFFFFFFFFFFF80，即 -128，写入 r1</t>
+  </si>
+  <si>
+    <t>从 r8 指向的内存读取 4 字节，得到 0x00000080。符号扩展后为 128，写入 r1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>从 r8 指向的内存读取 1 字节 0x80。LBU 零扩展得到 0x0000000000000080，即 128，写入 r1</t>
+  </si>
+  <si>
+    <t>将 BUFFER 的地址 0x80 加到 r0 后写入 r8，使 r8 指向 BUFFER</t>
+  </si>
+  <si>
+    <t>将 r1 中 0x00000080 写入 r8 指向的 BUFFER，其值由 300 变为 128</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较 r0 和 r0，两者相等，跳转到 PROG2，则 PC 指向 0x20</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 r1 和 r2 的值相加，结果 0x0000000000000080 写入 r3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 r1 和 r2 的值进行有符号乘法，结果为 0，将乘积的高 64 位写入 HI，低 64 位写入 LO，两者均为 0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较 r0 和 r0，两者相等，跳转到 PROG3，则 PC 指向 0x30</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 r1 和 r2 的值按位与，0x80 与 0 得到 0，写入 r3</t>
+  </si>
+  <si>
+    <t>比较 r0 和 r0，两者相等，跳转到 PROG4，则 PC 指向 0x40</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较 r1 和 r2 不相等则不跳转，PC 指向 0x44</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>空操作，顺序执行，则 PC 指向 0x48</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>空操作，顺序执行，则 PC 指向 0x4C</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1 为正值，跳转到 LABEL2，PC 指向 0x58</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1 为正值，跳转到 LABEL3，PC 指向 0x64，并将返回地址 0x5C 写入 r31</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 LABEL4 的地址 0x74 加到 r0 后写入 r1，使 r1 指向 LABEL4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将返回地址 0x6C 写入 r3，并跳转到 r1 保存的地址 0x74</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较 r0 和 r0，两者相等，触发陷阱并停止执行，模拟器中该步完成后 PC 变为 0x78</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 r1 的值与指令中的立即数按位与，得到 0，写入 r3，但ANDI 的立即数字段为 16 位，源码常量超出该范围，模拟器按低16位 &amp;0 处理</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +436,44 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -264,7 +497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -273,6 +506,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,17 +840,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963BAFC4-35B8-4FEE-93E9-AB146445FF59}">
   <dimension ref="A1:L60"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.21875" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="12" max="12" width="34.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" customWidth="1"/>
+    <col min="12" max="12" width="126.44140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -633,291 +883,1008 @@
       <c r="K1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="81.599999999999994" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" t="s">
+        <v>55</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L29" s="7"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J31" t="s">
+        <v>53</v>
+      </c>
+      <c r="K31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" t="s">
+        <v>53</v>
+      </c>
+      <c r="J32" t="s">
+        <v>53</v>
+      </c>
+      <c r="K32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" t="s">
+        <v>53</v>
+      </c>
+      <c r="J35" t="s">
+        <v>53</v>
+      </c>
+      <c r="K35" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L39" s="7"/>
+    </row>
+    <row r="40" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" t="s">
+        <v>79</v>
+      </c>
+      <c r="K40" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L41" s="7"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L42" s="7"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L44" s="7"/>
+    </row>
+    <row r="45" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" t="s">
+        <v>53</v>
+      </c>
+      <c r="I45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" t="s">
+        <v>79</v>
+      </c>
+      <c r="K45" t="s">
+        <v>55</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" t="s">
+        <v>53</v>
+      </c>
+      <c r="J46" t="s">
+        <v>79</v>
+      </c>
+      <c r="K46" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L47" s="7"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L50" s="7"/>
+    </row>
+    <row r="51" spans="1:12" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" t="s">
+        <v>53</v>
+      </c>
+      <c r="I51" t="s">
+        <v>53</v>
+      </c>
+      <c r="J51" t="s">
+        <v>79</v>
+      </c>
+      <c r="K51" t="s">
+        <v>55</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L52" s="7"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
     </row>
-    <row r="54" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L55" s="7"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L56" s="7"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L57" s="7"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L58" s="7"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="L59" s="7"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="L60" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>